--- a/tools/importer/reports/import-wknd-search.report.xlsx
+++ b/tools/importer/reports/import-wknd-search.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="211">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,7 +61,7 @@
     <t>wknd-about-us</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:17.016Z</t>
+    <t>2026-08-11T06:03:14.902Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -73,7 +73,7 @@
     <t>adventures.report.json</t>
   </si>
   <si>
-    <t>["teaser-columns","cards-magazine"]</t>
+    <t>["teaser-columns","cards-adventures"]</t>
   </si>
   <si>
     <t>adventures</t>
@@ -82,7 +82,7 @@
     <t>wknd-adventures</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:25.541Z</t>
+    <t>2026-08-11T06:35:24.757Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -145,7 +145,7 @@
     <t>wknd-faqs</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:22.340Z</t>
+    <t>2026-08-11T06:03:25.152Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -163,7 +163,7 @@
     <t>wknd-footer</t>
   </si>
   <si>
-    <t>2026-08-10T10:18:15.420Z</t>
+    <t>2026-08-12T11:10:55.259Z</t>
   </si>
   <si>
     <t>Footer</t>
@@ -184,7 +184,7 @@
     <t>wknd-home</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:53.844Z</t>
+    <t>2026-08-11T06:06:15.138Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -196,7 +196,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-08-07T07:38:58.174Z</t>
+    <t>2026-08-11T06:22:12.226Z</t>
   </si>
   <si>
     <t>nav.report.json</t>
@@ -208,7 +208,7 @@
     <t>wknd-nav</t>
   </si>
   <si>
-    <t>2026-08-10T10:18:20.500Z</t>
+    <t>2026-08-12T11:10:49.807Z</t>
   </si>
   <si>
     <t>Nav</t>
@@ -232,7 +232,7 @@
     <t>adventures/bali-surf-camp.report.json</t>
   </si>
   <si>
-    <t>["trip-details"]</t>
+    <t>["trip-details","tabs"]</t>
   </si>
   <si>
     <t>adventures/bali-surf-camp</t>
@@ -241,7 +241,7 @@
     <t>wknd-adventure</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:36.977Z</t>
+    <t>2026-08-11T05:38:36.943Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -256,7 +256,7 @@
     <t>adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:42.492Z</t>
+    <t>2026-08-11T05:38:43.191Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -271,7 +271,7 @@
     <t>adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:47.536Z</t>
+    <t>2026-08-11T05:38:49.328Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -286,7 +286,7 @@
     <t>adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:51.409Z</t>
+    <t>2026-08-11T05:38:55.058Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -301,7 +301,7 @@
     <t>adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-08-10T09:12:56.494Z</t>
+    <t>2026-08-11T05:39:00.011Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -316,7 +316,7 @@
     <t>adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:02.557Z</t>
+    <t>2026-08-11T05:39:05.111Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -331,7 +331,7 @@
     <t>adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:08.173Z</t>
+    <t>2026-08-11T05:39:11.402Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -346,7 +346,7 @@
     <t>adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:14.040Z</t>
+    <t>2026-08-11T05:39:15.940Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -361,7 +361,7 @@
     <t>adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:17.708Z</t>
+    <t>2026-08-11T05:39:21.279Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -376,7 +376,7 @@
     <t>adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:21.775Z</t>
+    <t>2026-08-11T05:39:26.898Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -391,7 +391,7 @@
     <t>adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:26.308Z</t>
+    <t>2026-08-11T05:39:32.274Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -406,7 +406,7 @@
     <t>adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:32.129Z</t>
+    <t>2026-08-11T05:39:37.156Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -421,7 +421,7 @@
     <t>adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:37.130Z</t>
+    <t>2026-08-11T05:39:43.313Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -436,7 +436,7 @@
     <t>adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:42.835Z</t>
+    <t>2026-08-11T05:39:47.535Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -451,7 +451,7 @@
     <t>adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:49.554Z</t>
+    <t>2026-08-11T05:39:54.118Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -466,7 +466,7 @@
     <t>adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-08-10T09:13:53.956Z</t>
+    <t>2026-08-11T05:39:59.135Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -511,7 +511,7 @@
     <t>magazine/arctic-surfing</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:26.685Z</t>
+    <t>2026-08-11T06:19:20.905Z</t>
   </si>
   <si>
     <t>magazine/guide-la-skateparks.report.json</t>
@@ -520,7 +520,7 @@
     <t>magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:31.643Z</t>
+    <t>2026-08-11T06:19:26.676Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -535,7 +535,7 @@
     <t>magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:35.685Z</t>
+    <t>2026-08-11T06:19:33.009Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -550,7 +550,7 @@
     <t>magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:39.945Z</t>
+    <t>2026-08-11T06:19:38.359Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -565,13 +565,67 @@
     <t>magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-08-07T09:09:44.331Z</t>
+    <t>2026-08-11T06:19:43.878Z</t>
   </si>
   <si>
     <t>Western Australia</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/western-australia.html</t>
+  </si>
+  <si>
+    <t>us/en.report.json</t>
+  </si>
+  <si>
+    <t>us/en</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:23.761Z</t>
+  </si>
+  <si>
+    <t>us/en/about-us.report.json</t>
+  </si>
+  <si>
+    <t>us/en/about-us</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:28.532Z</t>
+  </si>
+  <si>
+    <t>us/en/adventures.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:44.946Z</t>
+  </si>
+  <si>
+    <t>us/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>us/en/faqs</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:39.124Z</t>
+  </si>
+  <si>
+    <t>us/en/magazine.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:10:33.825Z</t>
+  </si>
+  <si>
+    <t>us/en/search.report.json</t>
+  </si>
+  <si>
+    <t>us/en/search</t>
+  </si>
+  <si>
+    <t>2026-08-12T11:11:00.753Z</t>
   </si>
   <si>
     <t>us/en/adventures/yosemite-backpacking.html.report.json</t>
@@ -980,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -2083,30 +2137,222 @@
         <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
         <v>188</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>56</v>
+      </c>
+      <c r="H35" t="s">
         <v>189</v>
       </c>
-      <c r="E35" t="s">
+      <c r="I35" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>190</v>
       </c>
-      <c r="F35" t="s">
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
         <v>191</v>
       </c>
-      <c r="G35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
         <v>192</v>
       </c>
-      <c r="I35" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" t="s">
+        <v>195</v>
+      </c>
+      <c r="I37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" t="s">
+        <v>198</v>
+      </c>
+      <c r="I38" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>200</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H39" t="s">
+        <v>201</v>
+      </c>
+      <c r="I39" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" t="s">
+        <v>204</v>
+      </c>
+      <c r="I40" t="s">
+        <v>71</v>
+      </c>
+      <c r="J40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" t="s">
+        <v>210</v>
+      </c>
+      <c r="I41" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" t="s">
         <v>153</v>
       </c>
     </row>
